--- a/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>AHR</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,148 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>504600</v>
+      </c>
+      <c r="E8" s="3">
         <v>499500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>482600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>464200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>467600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>452200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>452600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>426200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>388300</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>402600</v>
+      </c>
+      <c r="E9" s="3">
         <v>403600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>385000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>374600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>372500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>370100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>360800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>337500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>296100</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E10" s="3">
         <v>95900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>97600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>89600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>95100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>82100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>91800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>88700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>92200</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +822,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -838,8 +852,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,66 +884,75 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>4100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>15500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>13900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>41000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>22700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E15" s="3">
         <v>42800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>44000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>49300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>44700</v>
       </c>
       <c r="H15" s="3">
         <v>44700</v>
       </c>
       <c r="I15" s="3">
+        <v>44700</v>
+      </c>
+      <c r="J15" s="3">
         <v>45300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>40400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,66 +961,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>472900</v>
+      </c>
+      <c r="E17" s="3">
         <v>476000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>468800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>463700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>444600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>443400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>473700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>425100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>380500</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E18" s="3">
         <v>23500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>13800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>23000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-21100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,141 +1039,154 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>7600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>34100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>18100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>78100</v>
+      </c>
+      <c r="E21" s="3">
         <v>73800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>53200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>83900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>73300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>55300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>30300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>59700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E22" s="3">
         <v>33800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>40300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>40800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>40100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>38100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>34300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>26800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-31100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-27500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-49200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15300</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>700</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>300</v>
       </c>
       <c r="G24" s="3">
         <v>300</v>
       </c>
       <c r="H24" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I24" s="3">
         <v>100</v>
@@ -1149,10 +1195,13 @@
         <v>100</v>
       </c>
       <c r="K24" s="3">
+        <v>100</v>
+      </c>
+      <c r="L24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1229,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-31000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-27600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-49300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-15500</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-27400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-47500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1325,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1357,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1389,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,66 +1421,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-34100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-18100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-27400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-47500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1517,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-27400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-47500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1602,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,37 +1616,41 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E41" s="3">
         <v>77000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>43400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>35200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>48400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>41300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>65100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>79400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,37 +1678,43 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E43" s="3">
         <v>215900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>185400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>169500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>145700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>143700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>137500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>136000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>136800</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1646,8 +1742,11 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1675,8 +1774,11 @@
       <c r="K45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1704,8 +1806,11 @@
       <c r="K46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1713,86 +1818,95 @@
         <v>107400</v>
       </c>
       <c r="E47" s="3">
+        <v>107400</v>
+      </c>
+      <c r="F47" s="3">
         <v>107500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>106700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>106200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>99400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>92600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>91500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3686900</v>
+      </c>
+      <c r="E48" s="3">
         <v>3700300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3653300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3664600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3747100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3839100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3858000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3789100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3606300</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>414400</v>
+      </c>
+      <c r="E49" s="3">
         <v>422800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>415400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>431800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>445600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>454200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>467900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>492900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>447600</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +1934,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +1966,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>137100</v>
+      </c>
+      <c r="E52" s="3">
         <v>134000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>131900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>130800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>128000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>129800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>123900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>129000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>131100</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2030,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4644600</v>
+      </c>
+      <c r="E54" s="3">
         <v>4703400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4577900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4588900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4666400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4747700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4786700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4758600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4523900</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2078,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,37 +2092,41 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>253700</v>
+      </c>
+      <c r="E57" s="3">
         <v>257300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>242900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>233900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>223600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>231500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>243800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>235500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2020,37 +2154,43 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>178600</v>
+      </c>
+      <c r="E59" s="3">
         <v>219800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>225500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>231100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>262700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>268600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>273100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>260400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2078,37 +2218,43 @@
       <c r="K60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2052900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2028800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2568100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2536500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2566300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2594700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2560000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2472000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2422300</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2136,8 +2282,11 @@
       <c r="K62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2314,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2346,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2378,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2711200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2742500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3307600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3274700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3330600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3384000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3386600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3291400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3006700</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2426,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2456,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2488,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2520,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2552,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1344300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1313200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1276200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1232200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1209600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1180700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1138300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1064300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1024300</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2616,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2648,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2680,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1933400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1960900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1270300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1314200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1335800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1363700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1400100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1467300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1517200</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +2744,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-27400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-47500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +2829,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E83" s="3">
         <v>42800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>44000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>49300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>44700</v>
       </c>
       <c r="H83" s="3">
         <v>44700</v>
       </c>
       <c r="I83" s="3">
+        <v>44700</v>
+      </c>
+      <c r="J83" s="3">
         <v>45200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>40400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +2891,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +2923,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +2955,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +2987,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3019,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>59400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>25800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>29100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>19800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>23900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>34300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>57300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3067,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-55400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-31200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-33200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-69900</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3129,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3161,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-60300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>11000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>43000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-33300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,13 +3209,14 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-16600</v>
+        <v>-33000</v>
       </c>
       <c r="E96" s="3">
         <v>-16600</v>
@@ -2994,19 +3228,22 @@
         <v>-16600</v>
       </c>
       <c r="H96" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="I96" s="3">
         <v>-26500</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3271,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3303,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,37 +3335,43 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E100" s="3">
         <v>45000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-51600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-57300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-50900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3133,50 +3382,56 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E102" s="3">
         <v>33700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-23700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>20100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>AHR</t>
   </si>
@@ -656,161 +656,174 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>504600</v>
+        <v>521700</v>
       </c>
       <c r="E8" s="3">
-        <v>499500</v>
+        <v>503500</v>
       </c>
       <c r="F8" s="3">
-        <v>482600</v>
+        <v>498300</v>
       </c>
       <c r="G8" s="3">
-        <v>464200</v>
+        <v>481800</v>
       </c>
       <c r="H8" s="3">
-        <v>467600</v>
+        <v>462700</v>
       </c>
       <c r="I8" s="3">
-        <v>452200</v>
+        <v>461100</v>
       </c>
       <c r="J8" s="3">
+        <v>451900</v>
+      </c>
+      <c r="K8" s="3">
         <v>452600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>426200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>388300</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>402600</v>
+        <v>430900</v>
       </c>
       <c r="E9" s="3">
-        <v>403600</v>
+        <v>415900</v>
       </c>
       <c r="F9" s="3">
-        <v>385000</v>
+        <v>417400</v>
       </c>
       <c r="G9" s="3">
-        <v>374600</v>
+        <v>401600</v>
       </c>
       <c r="H9" s="3">
-        <v>372500</v>
+        <v>390200</v>
       </c>
       <c r="I9" s="3">
-        <v>370100</v>
+        <v>387200</v>
       </c>
       <c r="J9" s="3">
+        <v>385300</v>
+      </c>
+      <c r="K9" s="3">
         <v>360800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>337500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>296100</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>102000</v>
+        <v>90800</v>
       </c>
       <c r="E10" s="3">
-        <v>95900</v>
+        <v>87700</v>
       </c>
       <c r="F10" s="3">
-        <v>97600</v>
+        <v>81000</v>
       </c>
       <c r="G10" s="3">
-        <v>89600</v>
+        <v>80100</v>
       </c>
       <c r="H10" s="3">
-        <v>95100</v>
+        <v>72500</v>
       </c>
       <c r="I10" s="3">
-        <v>82100</v>
+        <v>73900</v>
       </c>
       <c r="J10" s="3">
+        <v>66600</v>
+      </c>
+      <c r="K10" s="3">
         <v>91800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>88700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>92200</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -823,8 +836,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -855,8 +869,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,72 +904,81 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="E14" s="3">
-        <v>4100</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>15500</v>
+        <v>500</v>
       </c>
       <c r="G14" s="3">
-        <v>13900</v>
+        <v>9200</v>
       </c>
       <c r="H14" s="3">
-        <v>900</v>
+        <v>-20500</v>
       </c>
       <c r="I14" s="3">
-        <v>300</v>
+        <v>-3400</v>
       </c>
       <c r="J14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K14" s="3">
         <v>41000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>22700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E15" s="3">
         <v>45300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>42800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>44000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>49300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>44700</v>
       </c>
       <c r="I15" s="3">
         <v>44700</v>
       </c>
       <c r="J15" s="3">
+        <v>44700</v>
+      </c>
+      <c r="K15" s="3">
         <v>45300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>40400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,72 +988,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>487100</v>
+      </c>
+      <c r="E17" s="3">
         <v>472900</v>
       </c>
-      <c r="E17" s="3">
-        <v>476000</v>
-      </c>
       <c r="F17" s="3">
-        <v>468800</v>
+        <v>472000</v>
       </c>
       <c r="G17" s="3">
-        <v>463700</v>
+        <v>456900</v>
       </c>
       <c r="H17" s="3">
-        <v>444600</v>
+        <v>450800</v>
       </c>
       <c r="I17" s="3">
-        <v>443400</v>
+        <v>443700</v>
       </c>
       <c r="J17" s="3">
+        <v>443100</v>
+      </c>
+      <c r="K17" s="3">
         <v>473700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>425100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>380500</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>31700</v>
+        <v>34600</v>
       </c>
       <c r="E18" s="3">
-        <v>23500</v>
+        <v>30600</v>
       </c>
       <c r="F18" s="3">
-        <v>13800</v>
+        <v>26400</v>
       </c>
       <c r="G18" s="3">
-        <v>500</v>
+        <v>24800</v>
       </c>
       <c r="H18" s="3">
-        <v>23000</v>
+        <v>11900</v>
       </c>
       <c r="I18" s="3">
-        <v>8800</v>
+        <v>17400</v>
       </c>
       <c r="J18" s="3">
+        <v>8900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-21100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,156 +1073,169 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1100</v>
+        <v>4100</v>
       </c>
       <c r="E20" s="3">
-        <v>7600</v>
+        <v>-3600</v>
       </c>
       <c r="F20" s="3">
-        <v>-4500</v>
+        <v>-7900</v>
       </c>
       <c r="G20" s="3">
-        <v>34100</v>
+        <v>5500</v>
       </c>
       <c r="H20" s="3">
-        <v>5500</v>
+        <v>-3500</v>
       </c>
       <c r="I20" s="3">
-        <v>1900</v>
+        <v>-8700</v>
       </c>
       <c r="J20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K20" s="3">
         <v>6200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>18100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>78100</v>
+        <v>74700</v>
       </c>
       <c r="E21" s="3">
-        <v>73800</v>
+        <v>79500</v>
       </c>
       <c r="F21" s="3">
-        <v>53200</v>
+        <v>77000</v>
       </c>
       <c r="G21" s="3">
-        <v>83900</v>
+        <v>63300</v>
       </c>
       <c r="H21" s="3">
-        <v>73300</v>
+        <v>64600</v>
       </c>
       <c r="I21" s="3">
-        <v>55300</v>
+        <v>70800</v>
       </c>
       <c r="J21" s="3">
+        <v>55900</v>
+      </c>
+      <c r="K21" s="3">
         <v>30300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>59700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>29200</v>
+        <v>30400</v>
       </c>
       <c r="E22" s="3">
-        <v>33800</v>
+        <v>30600</v>
       </c>
       <c r="F22" s="3">
-        <v>40300</v>
+        <v>36400</v>
       </c>
       <c r="G22" s="3">
-        <v>40800</v>
+        <v>41200</v>
       </c>
       <c r="H22" s="3">
-        <v>40100</v>
+        <v>42000</v>
       </c>
       <c r="I22" s="3">
-        <v>38100</v>
+        <v>41000</v>
       </c>
       <c r="J22" s="3">
+        <v>39000</v>
+      </c>
+      <c r="K22" s="3">
         <v>34300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>26800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E23" s="3">
         <v>3600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-31100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-11500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-27500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-49200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15300</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>300</v>
       </c>
       <c r="H24" s="3">
         <v>300</v>
       </c>
       <c r="I24" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
@@ -1198,10 +1244,13 @@
         <v>100</v>
       </c>
       <c r="L24" s="3">
+        <v>100</v>
+      </c>
+      <c r="M24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1281,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E26" s="3">
         <v>2900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-31000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-27600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-49300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15500</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E27" s="3">
         <v>2000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-27400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-47500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1386,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1421,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1456,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,72 +1491,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1100</v>
+        <v>-4100</v>
       </c>
       <c r="E32" s="3">
-        <v>-7600</v>
+        <v>3600</v>
       </c>
       <c r="F32" s="3">
-        <v>4500</v>
+        <v>7900</v>
       </c>
       <c r="G32" s="3">
-        <v>-34100</v>
+        <v>-5500</v>
       </c>
       <c r="H32" s="3">
-        <v>-5500</v>
+        <v>3500</v>
       </c>
       <c r="I32" s="3">
-        <v>-1900</v>
+        <v>8700</v>
       </c>
       <c r="J32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-6200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-18100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E33" s="3">
         <v>2000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-27400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-47500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1596,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E35" s="3">
         <v>2000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-27400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-47500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1688,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,40 +1703,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E41" s="3">
         <v>52100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>77000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>43400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>35200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>48400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>41300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>65100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>79400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1658,19 +1748,19 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -1681,63 +1771,69 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>201000</v>
+        <v>253900</v>
       </c>
       <c r="E43" s="3">
-        <v>215900</v>
+        <v>250300</v>
       </c>
       <c r="F43" s="3">
-        <v>185400</v>
+        <v>264400</v>
       </c>
       <c r="G43" s="3">
-        <v>169500</v>
+        <v>232900</v>
       </c>
       <c r="H43" s="3">
-        <v>145700</v>
+        <v>216400</v>
       </c>
       <c r="I43" s="3">
-        <v>143700</v>
+        <v>194200</v>
       </c>
       <c r="J43" s="3">
+        <v>191700</v>
+      </c>
+      <c r="K43" s="3">
         <v>137500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>136000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>136800</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>20200</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>20700</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>19300</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>19100</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1745,31 +1841,34 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>37100</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>33200</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>33800</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>31100</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>31200</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -1777,31 +1876,34 @@
       <c r="L45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>423800</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>410900</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>447900</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>377800</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>362600</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>343100</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>330200</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -1809,104 +1911,116 @@
       <c r="L46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>107400</v>
+        <v>106400</v>
       </c>
       <c r="E47" s="3">
         <v>107400</v>
       </c>
       <c r="F47" s="3">
+        <v>107400</v>
+      </c>
+      <c r="G47" s="3">
         <v>107500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>106700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>106200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>99400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>92600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>91500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3709000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3686900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3700300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3653300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3664600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3747100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3839100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3858000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3789100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3606300</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>412700</v>
+      </c>
+      <c r="E49" s="3">
         <v>414400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>422800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>415400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>431800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>445600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>454200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>467900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>492900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>447600</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2051,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2086,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>137100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>134000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>131900</v>
-      </c>
-      <c r="G52" s="3">
-        <v>130800</v>
-      </c>
-      <c r="H52" s="3">
-        <v>128000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>129800</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>123900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>129000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>131100</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2156,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4677000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4644600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4703400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4577900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4588900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4666400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4747700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4786700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4758600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4523900</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2208,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,63 +2223,67 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>253700</v>
+        <v>82900</v>
       </c>
       <c r="E57" s="3">
-        <v>257300</v>
+        <v>79400</v>
       </c>
       <c r="F57" s="3">
-        <v>242900</v>
+        <v>108400</v>
       </c>
       <c r="G57" s="3">
-        <v>233900</v>
+        <v>90700</v>
       </c>
       <c r="H57" s="3">
-        <v>223600</v>
+        <v>85700</v>
       </c>
       <c r="I57" s="3">
-        <v>231500</v>
+        <v>74200</v>
       </c>
       <c r="J57" s="3">
+        <v>81300</v>
+      </c>
+      <c r="K57" s="3">
         <v>243800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>235500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>46100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>170500</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>414700</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>657200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>380800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>399600</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>493500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2157,63 +2291,69 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>178600</v>
+        <v>61300</v>
       </c>
       <c r="E59" s="3">
-        <v>219800</v>
+        <v>55500</v>
       </c>
       <c r="F59" s="3">
-        <v>225500</v>
+        <v>33700</v>
       </c>
       <c r="G59" s="3">
-        <v>231100</v>
+        <v>42500</v>
       </c>
       <c r="H59" s="3">
-        <v>262700</v>
+        <v>39100</v>
       </c>
       <c r="I59" s="3">
-        <v>268600</v>
+        <v>43000</v>
       </c>
       <c r="J59" s="3">
+        <v>43800</v>
+      </c>
+      <c r="K59" s="3">
         <v>273100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>260400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>316100</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>424700</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>672800</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>901200</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>618000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>623900</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>726200</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2221,63 +2361,69 @@
       <c r="L60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2052900</v>
+        <v>2049300</v>
       </c>
       <c r="E61" s="3">
-        <v>2028800</v>
+        <v>2061000</v>
       </c>
       <c r="F61" s="3">
-        <v>2568100</v>
+        <v>1833900</v>
       </c>
       <c r="G61" s="3">
-        <v>2536500</v>
+        <v>2136400</v>
       </c>
       <c r="H61" s="3">
-        <v>2566300</v>
+        <v>2386800</v>
       </c>
       <c r="I61" s="3">
-        <v>2594700</v>
+        <v>2429400</v>
       </c>
       <c r="J61" s="3">
+        <v>2369900</v>
+      </c>
+      <c r="K61" s="3">
         <v>2560000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2472000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2422300</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>30900</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>31700</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>31400</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>42300</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>29500</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>34600</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>42500</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -2285,8 +2431,11 @@
       <c r="L62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2466,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2501,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2536,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2711200</v>
+        <v>2419800</v>
       </c>
       <c r="E66" s="3">
-        <v>2742500</v>
+        <v>2540500</v>
       </c>
       <c r="F66" s="3">
-        <v>3307600</v>
+        <v>2560600</v>
       </c>
       <c r="G66" s="3">
-        <v>3274700</v>
+        <v>3118800</v>
       </c>
       <c r="H66" s="3">
-        <v>3330600</v>
+        <v>3055200</v>
       </c>
       <c r="I66" s="3">
-        <v>3384000</v>
+        <v>3110100</v>
       </c>
       <c r="J66" s="3">
+        <v>3160800</v>
+      </c>
+      <c r="K66" s="3">
         <v>3386600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3291400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3006700</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2588,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2621,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2656,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2691,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2726,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1386800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1344300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1313200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1276200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1232200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1209600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1180700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1138300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1064300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1024300</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2796,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +2831,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +2866,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2207500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1933400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1960900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1270300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1314200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1335800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1363700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1400100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1467300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1517200</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +2936,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E81" s="3">
         <v>2000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-27400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-47500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,40 +3028,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>45300</v>
+        <v>45600</v>
       </c>
       <c r="E83" s="3">
-        <v>42800</v>
+        <v>55100</v>
       </c>
       <c r="F83" s="3">
-        <v>44000</v>
+        <v>36700</v>
       </c>
       <c r="G83" s="3">
-        <v>49300</v>
+        <v>57300</v>
       </c>
       <c r="H83" s="3">
-        <v>44700</v>
+        <v>29000</v>
       </c>
       <c r="I83" s="3">
-        <v>44700</v>
+        <v>42000</v>
       </c>
       <c r="J83" s="3">
+        <v>35200</v>
+      </c>
+      <c r="K83" s="3">
         <v>45200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>40400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3096,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3131,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3166,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3201,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3236,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E89" s="3">
         <v>59400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>25800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>29100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>19800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>23900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>34300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>57300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3288,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-64600</v>
+        <v>-23900</v>
       </c>
       <c r="E91" s="3">
-        <v>-20200</v>
+        <v>-18500</v>
       </c>
       <c r="F91" s="3">
-        <v>-25400</v>
+        <v>-19900</v>
       </c>
       <c r="G91" s="3">
-        <v>-55400</v>
+        <v>74400</v>
       </c>
       <c r="H91" s="3">
-        <v>-31200</v>
+        <v>-22300</v>
       </c>
       <c r="I91" s="3">
-        <v>-33200</v>
+        <v>-30600</v>
       </c>
       <c r="J91" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-18300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-69900</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3356,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3391,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-60300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>11000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>43000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-33300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,31 +3443,32 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-33000</v>
+        <v>33000</v>
       </c>
       <c r="E96" s="3">
-        <v>-16600</v>
+        <v>33000</v>
       </c>
       <c r="F96" s="3">
-        <v>-16600</v>
+        <v>16600</v>
       </c>
       <c r="G96" s="3">
-        <v>-16600</v>
+        <v>16600</v>
       </c>
       <c r="H96" s="3">
-        <v>-16600</v>
+        <v>16600</v>
       </c>
       <c r="I96" s="3">
-        <v>-26500</v>
+        <v>16600</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>26500</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3242,8 +3476,11 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3511,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3546,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,100 +3581,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-26000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>45000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-51600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-57300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-50900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G101" s="3">
+        <v>200</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-26900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>33700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-23700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>20100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>AHR</t>
   </si>
@@ -656,174 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>540200</v>
+      </c>
+      <c r="E8" s="3">
         <v>521700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>503500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>498300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>481800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>462700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>461100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>451900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>452600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>426200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>388300</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>444400</v>
+      </c>
+      <c r="E9" s="3">
         <v>430900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>415900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>417400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>401600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>390200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>387200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>385300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>360800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>337500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>296100</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>95800</v>
+      </c>
+      <c r="E10" s="3">
         <v>90800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>87700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>81000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>80100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>72500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>73900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>66600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>91800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>88700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>92200</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -837,8 +849,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -872,8 +885,11 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,78 +923,87 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E14" s="3">
         <v>2900</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>9200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-20500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-3400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>41000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>22700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E15" s="3">
         <v>44200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>45300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>42800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>44000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>49300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>44700</v>
       </c>
       <c r="J15" s="3">
         <v>44700</v>
       </c>
       <c r="K15" s="3">
+        <v>44700</v>
+      </c>
+      <c r="L15" s="3">
         <v>45300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>40400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,78 +1014,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>503400</v>
+      </c>
+      <c r="E17" s="3">
         <v>487100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>472900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>472000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>456900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>450800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>443700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>443100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>473700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>425100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>380500</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E18" s="3">
         <v>34600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>30600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>26400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>24800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>17400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-21100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,171 +1106,184 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E20" s="3">
         <v>4100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>18100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>88100</v>
+      </c>
+      <c r="E21" s="3">
         <v>74700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>79500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>77000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>63300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>64600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>70800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>55900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>30300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>59700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E22" s="3">
         <v>30400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>30600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>36400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>41200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>42000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>41000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>39000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>34300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>26800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-31100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-27500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-49200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15300</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>300</v>
       </c>
       <c r="I24" s="3">
         <v>300</v>
       </c>
       <c r="J24" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
@@ -1247,10 +1292,13 @@
         <v>100</v>
       </c>
       <c r="M24" s="3">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,78 +1332,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-27600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-49300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15500</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-27400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-47500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1446,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1484,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1522,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,78 +1560,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-18100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-27400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-47500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,83 +1674,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-27400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-47500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1773,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,67 +1789,71 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E41" s="3">
         <v>67900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>52100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>77000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>43400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>35200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>48400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>41300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>65100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>79400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>5900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -1774,253 +1863,277 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>258600</v>
+      </c>
+      <c r="E43" s="3">
         <v>253900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>250300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>264400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>232900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>216400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>194200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>191700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>137500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>136000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>136800</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E44" s="3">
         <v>20200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>20000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>20700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>19500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>22000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>19300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>19100</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E45" s="3">
         <v>33000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>37100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>32700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>31100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31200</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>432300</v>
+      </c>
+      <c r="E46" s="3">
         <v>423800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>410900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>447900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>377800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>362600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>343100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>330200</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>105200</v>
+      </c>
+      <c r="E47" s="3">
         <v>106400</v>
-      </c>
-      <c r="E47" s="3">
-        <v>107400</v>
       </c>
       <c r="F47" s="3">
         <v>107400</v>
       </c>
       <c r="G47" s="3">
+        <v>107400</v>
+      </c>
+      <c r="H47" s="3">
         <v>107500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>106700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>106200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>99400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>92600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>91500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3530600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3709000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3686900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3700300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3653300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3664600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3747100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3839100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3858000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3789100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3606300</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>396400</v>
+      </c>
+      <c r="E49" s="3">
         <v>412700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>414400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>422800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>415400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>431800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>445600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>454200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>467900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>492900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>447600</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2167,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,8 +2205,11 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2115,17 +2234,20 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>123900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>129000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>131100</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2281,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4488100</v>
+      </c>
+      <c r="E54" s="3">
         <v>4677000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4644600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4703400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4577900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4588900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4666400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4747700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4786700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4758600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4523900</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2337,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,218 +2353,237 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E57" s="3">
         <v>82900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>79400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>108400</v>
       </c>
-      <c r="G57" s="3">
-        <v>90700</v>
-      </c>
       <c r="H57" s="3">
+        <v>89600</v>
+      </c>
+      <c r="I57" s="3">
         <v>85700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>74200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>81300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>243800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>235500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E58" s="3">
         <v>46100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>170500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>414700</v>
       </c>
-      <c r="G58" s="3">
-        <v>657200</v>
-      </c>
       <c r="H58" s="3">
+        <v>312200</v>
+      </c>
+      <c r="I58" s="3">
         <v>380800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>399600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>493500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E59" s="3">
         <v>61300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>55500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>33700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>42500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>39100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>43000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>43800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>273100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>260400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>323500</v>
+      </c>
+      <c r="E60" s="3">
         <v>316100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>424700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>672800</v>
       </c>
-      <c r="G60" s="3">
-        <v>901200</v>
-      </c>
       <c r="H60" s="3">
+        <v>555100</v>
+      </c>
+      <c r="I60" s="3">
         <v>618000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>623900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>726200</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1807200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2049300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2061000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1833900</v>
       </c>
-      <c r="G61" s="3">
-        <v>2136400</v>
-      </c>
       <c r="H61" s="3">
+        <v>2483800</v>
+      </c>
+      <c r="I61" s="3">
         <v>2386800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2429400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2369900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2560000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2472000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2422300</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E62" s="3">
         <v>30900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>31700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>31400</v>
       </c>
-      <c r="G62" s="3">
-        <v>42300</v>
-      </c>
       <c r="H62" s="3">
+        <v>41000</v>
+      </c>
+      <c r="I62" s="3">
         <v>29500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>34600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>42500</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2617,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2655,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2693,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2183900</v>
+      </c>
+      <c r="E66" s="3">
         <v>2419800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2540500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2560600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3118800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3055200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3110100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3160800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3386600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3291400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3006700</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2749,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2785,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2823,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +2861,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +2899,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1458100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1386800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1344300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1313200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1276200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1232200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1209600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1180700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1138300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1064300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1024300</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2975,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3013,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3051,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2261200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2207500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1933400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1960900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1270300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1314200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1335800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1363700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1400100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1467300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1517200</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,83 +3127,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-27400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-47500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,43 +3226,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E83" s="3">
         <v>45600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>55100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>36700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>57300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>29000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>42000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>35200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>45200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>40400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3300,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3338,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3376,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3414,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3452,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E89" s="3">
         <v>63100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>59400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>25800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>29100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>19800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>23900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>34300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>57300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,43 +3508,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-23900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19900</v>
       </c>
-      <c r="G91" s="3">
-        <v>74400</v>
-      </c>
       <c r="H91" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-22300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-30600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-18300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-69900</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3582,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +3620,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>87200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-30400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-60300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>11000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>43000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-33300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-25200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,19 +3676,20 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>33000</v>
+        <v>38300</v>
       </c>
       <c r="E96" s="3">
         <v>33000</v>
       </c>
       <c r="F96" s="3">
-        <v>16600</v>
+        <v>33000</v>
       </c>
       <c r="G96" s="3">
         <v>16600</v>
@@ -3468,19 +3701,22 @@
         <v>16600</v>
       </c>
       <c r="J96" s="3">
+        <v>16600</v>
+      </c>
+      <c r="K96" s="3">
         <v>26500</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3750,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3788,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,109 +3826,121 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-140000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-26000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>45000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-51600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-57300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-50900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-12000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E102" s="3">
         <v>19100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-26900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>33700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-23700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>20100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>AHR</t>
   </si>
@@ -656,186 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>538800</v>
+      </c>
+      <c r="E8" s="3">
         <v>540200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>521700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>503500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>498300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>481800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>462700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>461100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>451900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>452600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>426200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>388300</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>446100</v>
+      </c>
+      <c r="E9" s="3">
         <v>444400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>430900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>415900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>417400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>401600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>390200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>387200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>385300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>360800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>337500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>296100</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>92700</v>
+      </c>
+      <c r="E10" s="3">
         <v>95800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>90800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>87700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>81000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>80100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>72500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>73900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>66600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>91800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>88700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>92200</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,8 +863,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +902,11 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,84 +943,93 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E14" s="3">
         <v>42800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2900</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>9200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-20500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-3400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>41000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>22700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E15" s="3">
         <v>46900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>44200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>45300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>42800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>44000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>49300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>44700</v>
       </c>
       <c r="K15" s="3">
         <v>44700</v>
       </c>
       <c r="L15" s="3">
+        <v>44700</v>
+      </c>
+      <c r="M15" s="3">
         <v>45300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>40400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,84 +1041,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>500300</v>
+      </c>
+      <c r="E17" s="3">
         <v>503400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>487100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>472900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>472000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>456900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>450800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>443700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>443100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>473700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>425100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>380500</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E18" s="3">
         <v>36800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>34600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>30600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>26400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>24800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-21100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,186 +1140,199 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>18100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>81700</v>
+      </c>
+      <c r="E21" s="3">
         <v>88100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>74700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>79500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>77000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>63300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>64600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>70800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>55900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>30300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>59700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E22" s="3">
         <v>30300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>30400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>36400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>41200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>42000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>41000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>39000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>34300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>26800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-31900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-31100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-11500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-49200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15300</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>300</v>
       </c>
       <c r="J24" s="3">
         <v>300</v>
       </c>
       <c r="K24" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
@@ -1295,10 +1341,13 @@
         <v>100</v>
       </c>
       <c r="N24" s="3">
+        <v>100</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,84 +1384,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-32400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-11900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-27600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-49300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-15500</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-31800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-27400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-47500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,84 +1630,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E32" s="3">
         <v>4300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-18100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-31800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-27400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-47500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,89 +1753,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-31800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-27400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-47500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,73 +1876,77 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>86100</v>
+      </c>
+      <c r="E41" s="3">
         <v>76700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>67900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>52100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>77000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>43400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>35200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>48400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>65100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>79400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>600</v>
+      </c>
+      <c r="E42" s="3">
         <v>1000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>5900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4800</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -1866,274 +1956,298 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>271100</v>
+      </c>
+      <c r="E43" s="3">
         <v>258600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>253900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>250300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>264400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>232900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>216400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>194200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>191700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>137500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>136000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>136800</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E44" s="3">
         <v>19500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>20200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>20000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>20700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>19500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>22000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>19300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>19100</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E45" s="3">
         <v>29900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>33000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>32700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>31200</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>456000</v>
+      </c>
+      <c r="E46" s="3">
         <v>432300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>423800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>410900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>447900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>377800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>362600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>343100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>330200</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>103800</v>
+      </c>
+      <c r="E47" s="3">
         <v>105200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>106400</v>
-      </c>
-      <c r="F47" s="3">
-        <v>107400</v>
       </c>
       <c r="G47" s="3">
         <v>107400</v>
       </c>
       <c r="H47" s="3">
+        <v>107400</v>
+      </c>
+      <c r="I47" s="3">
         <v>107500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>106700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>106200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>99400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>92600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>91500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3490400</v>
+      </c>
+      <c r="E48" s="3">
         <v>3530600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3709000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3686900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3700300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3653300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3664600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3747100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3839100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3858000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3789100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3606300</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>391400</v>
+      </c>
+      <c r="E49" s="3">
         <v>396400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>412700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>414400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>422800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>415400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>431800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>445600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>454200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>467900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>492900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>447600</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,8 +2325,11 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2237,17 +2357,20 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>123900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>129000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>131100</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4464100</v>
+      </c>
+      <c r="E54" s="3">
         <v>4488100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4677000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4644600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4703400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4577900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4588900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4666400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4747700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4786700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4758600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4523900</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,236 +2484,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E57" s="3">
         <v>78700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>82900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>79400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>108400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>89600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>85700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>74200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>81300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>243800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>235500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E58" s="3">
         <v>64400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>46100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>170500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>414700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>312200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>380800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>399600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>493500</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>63800</v>
+      </c>
+      <c r="E59" s="3">
         <v>63700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>61300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>55500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>33700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>42500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>39100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>43000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>43800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>273100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>260400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>327300</v>
+      </c>
+      <c r="E60" s="3">
         <v>323500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>316100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>424700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>672800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>555100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>618000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>623900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>726200</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1778000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1807200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2049300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2061000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1833900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2483800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2386800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2429400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2369900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2560000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2472000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2422300</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E62" s="3">
         <v>13900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>30900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>31700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>31400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>41000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>29500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>34600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>42500</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2159300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2183900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2419800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2540500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2560600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3118800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3055200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3110100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3160800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3386600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3291400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3006700</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2864,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1504900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1458100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1386800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1344300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1313200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1276200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1232200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1209600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1180700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1138300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1064300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1024300</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2262400</v>
+      </c>
+      <c r="E76" s="3">
         <v>2261200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2207500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1933400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1960900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1270300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1314200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1335800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1363700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1400100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1467300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1517200</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,89 +3319,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-31800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-27400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-47500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,46 +3425,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E83" s="3">
         <v>49600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>45600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>55100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>36700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>57300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>29000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>42000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>35200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>45200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>40400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E89" s="3">
         <v>59500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>63100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>59400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>25800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>29100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>19800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>23900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>34300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>57300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,46 +3729,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-29700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-23900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18500</v>
       </c>
-      <c r="G91" s="3">
-        <v>-19900</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-25400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-22300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-30600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-21500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-18300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-69900</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,46 +3850,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-32800</v>
+      </c>
+      <c r="E94" s="3">
         <v>87200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-30400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-60300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>11000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>43000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-33300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-25200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,22 +3910,23 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E96" s="3">
         <v>38300</v>
-      </c>
-      <c r="E96" s="3">
-        <v>33000</v>
       </c>
       <c r="F96" s="3">
         <v>33000</v>
       </c>
       <c r="G96" s="3">
-        <v>16600</v>
+        <v>33000</v>
       </c>
       <c r="H96" s="3">
         <v>16600</v>
@@ -3704,19 +3938,22 @@
         <v>16600</v>
       </c>
       <c r="K96" s="3">
+        <v>16600</v>
+      </c>
+      <c r="L96" s="3">
         <v>26500</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,46 +4072,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-140000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-26000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>45000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-51600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-57300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-50900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3876,71 +4125,77 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E102" s="3">
         <v>6600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>19100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-26900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>33700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-23700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>20100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-15000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>AHR</t>
   </si>
@@ -656,199 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>541300</v>
+      </c>
+      <c r="E8" s="3">
         <v>538800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>540200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>521700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>503500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>498300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>481800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>462700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>461100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>451900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>452600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>426200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>388300</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>439300</v>
+      </c>
+      <c r="E9" s="3">
         <v>446100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>444400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>430900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>415900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>417400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>401600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>390200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>387200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>385300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>360800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>337500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>296100</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E10" s="3">
         <v>92700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>95800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>90800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>87700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>81000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>80100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>72500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>73900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>66600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>91800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>88700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>92200</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,90 +963,99 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E14" s="3">
         <v>23900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>42800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2900</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>9200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-20500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-3400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>41000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>22700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E15" s="3">
         <v>41100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>46900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>44200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>45300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>42800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>44000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>49300</v>
-      </c>
-      <c r="K15" s="3">
-        <v>44700</v>
       </c>
       <c r="L15" s="3">
         <v>44700</v>
       </c>
       <c r="M15" s="3">
+        <v>44700</v>
+      </c>
+      <c r="N15" s="3">
         <v>45300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>40400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>496200</v>
+      </c>
+      <c r="E17" s="3">
         <v>500300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>503400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>487100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>472900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>472000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>456900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>450800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>443700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>443100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>473700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>425100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>380500</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E18" s="3">
         <v>38400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>36800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>34600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>30600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>26400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>24800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-21100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,201 +1174,214 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-7900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>18100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>90600</v>
+      </c>
+      <c r="E21" s="3">
         <v>81700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>88100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>74700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>79500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>77000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>63300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>64600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>70800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>55900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>30300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>59700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E22" s="3">
         <v>22900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>30300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>30600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>36400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>41200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>42000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>41000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>39000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>34300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>26800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-31900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-31100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-49200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15300</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>700</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>300</v>
       </c>
       <c r="K24" s="3">
         <v>300</v>
       </c>
       <c r="L24" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M24" s="3">
         <v>100</v>
@@ -1344,10 +1390,13 @@
         <v>100</v>
       </c>
       <c r="O24" s="3">
+        <v>100</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-32400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-27600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-49300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15500</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-31800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-27400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-47500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,90 +1700,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E32" s="3">
         <v>2200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>7900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-18100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-31800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-27400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-47500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-31800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-27400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-47500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,79 +1963,83 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>133500</v>
+      </c>
+      <c r="E41" s="3">
         <v>86100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>76700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>67900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>52100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>77000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>48400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>41300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>65100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>79400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>500</v>
+      </c>
+      <c r="E42" s="3">
         <v>600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1000</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>5900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4800</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -1959,49 +2049,55 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>272800</v>
+      </c>
+      <c r="E43" s="3">
         <v>271100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>258600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>253900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>250300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>264400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>232900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>216400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>194200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>191700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>137500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>136000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>136800</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2009,245 +2105,263 @@
         <v>19400</v>
       </c>
       <c r="E44" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F44" s="3">
         <v>19500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>20200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>20000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>20700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>19500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>22000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>19300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>19100</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E45" s="3">
         <v>37500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>29900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>37100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>32700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>31100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31200</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>497600</v>
+      </c>
+      <c r="E46" s="3">
         <v>456000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>432300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>423800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>410900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>447900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>377800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>362600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>343100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>330200</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
       <c r="O46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E47" s="3">
         <v>103800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>105200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>106400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>107400</v>
       </c>
       <c r="H47" s="3">
         <v>107400</v>
       </c>
       <c r="I47" s="3">
+        <v>107400</v>
+      </c>
+      <c r="J47" s="3">
         <v>107500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>106700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>106200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>99400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>92600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>91500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3494000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3490400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3530600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3709000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3686900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3700300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3653300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3664600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3747100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3839100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3858000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3789100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3606300</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>390800</v>
+      </c>
+      <c r="E49" s="3">
         <v>391400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>396400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>412700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>414400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>422800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>415400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>431800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>445600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>454200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>467900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>492900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>447600</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,8 +2445,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2360,17 +2480,20 @@
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3">
         <v>123900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>129000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>131100</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4506700</v>
+      </c>
+      <c r="E54" s="3">
         <v>4464100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4488100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4677000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4644600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4703400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4577900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4588900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4666400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4747700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4786700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4758600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4523900</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,254 +2615,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>79400</v>
+      </c>
+      <c r="E57" s="3">
         <v>79100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>78700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>82900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>79400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>108400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>89600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>85700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>74200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>81300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>243800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>235500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E58" s="3">
         <v>54500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>64400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>46100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>170500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>414700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>312200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>380800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>399600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>493500</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>63300</v>
+      </c>
+      <c r="E59" s="3">
         <v>63800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>63700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>61300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>55500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>33700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>42500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>39100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>43000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>43800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>273100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>260400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>308700</v>
+      </c>
+      <c r="E60" s="3">
         <v>327300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>323500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>316100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>424700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>672800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>555100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>618000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>623900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>726200</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
       <c r="O60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1682800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1778000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1807200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2049300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2061000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1833900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2483800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2386800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2429400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2369900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2560000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2472000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2422300</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E62" s="3">
         <v>28100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>30900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>31700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>31400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>41000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>29500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>34600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>42500</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2044000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2159300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2183900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2419800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2540500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2560600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3118800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3055200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3110100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3160800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3386600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3291400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3006700</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1536300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1504900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1458100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1386800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1344300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1313200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1276200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1232200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1209600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1180700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1138300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1064300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1024300</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2421000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2262400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2261200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2207500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1933400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1960900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1270300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1314200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1335800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1363700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1400100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1467300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1517200</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-31800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-27400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-47500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,49 +3624,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E83" s="3">
         <v>37800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>49600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>55100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>36700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>57300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>29000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>42000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>35200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>45200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>40400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E89" s="3">
         <v>60600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>59500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>63100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>59400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>25800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>29100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>23900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>34300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>57300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,49 +3950,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="3">
+        <v>-48100</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-29700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-23900</v>
       </c>
-      <c r="G91" s="3">
-        <v>-18500</v>
-      </c>
-      <c r="H91" s="3" t="s">
+      <c r="H91" s="3">
+        <v>-38400</v>
+      </c>
+      <c r="I91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-25400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-22300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-30600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-21500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-18300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-69900</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-62100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-32800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>87200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-30400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-60300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>11000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>43000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-33300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-25200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,25 +4144,26 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E96" s="3">
         <v>39500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>38300</v>
-      </c>
-      <c r="F96" s="3">
-        <v>33000</v>
       </c>
       <c r="G96" s="3">
         <v>33000</v>
       </c>
       <c r="H96" s="3">
-        <v>16600</v>
+        <v>33000</v>
       </c>
       <c r="I96" s="3">
         <v>16600</v>
@@ -3941,19 +4175,22 @@
         <v>16600</v>
       </c>
       <c r="L96" s="3">
+        <v>16600</v>
+      </c>
+      <c r="M96" s="3">
         <v>26500</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,49 +4318,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-23800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-140000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-26000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>45000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-51600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-57300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-50900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-12000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4128,74 +4377,80 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E102" s="3">
         <v>4200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-26900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>33700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-23700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>20100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-15000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>AHR</t>
   </si>
@@ -656,225 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>604700</v>
+      </c>
+      <c r="E8" s="3">
         <v>573400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>541300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>538800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>540200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>521700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>503500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>498300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>481800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>462700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>461100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>451900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>452600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>426200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>388300</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>492500</v>
+      </c>
+      <c r="E9" s="3">
         <v>467100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>439300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>446100</v>
       </c>
-      <c r="G9" s="3">
-        <v>444400</v>
-      </c>
       <c r="H9" s="3">
+        <v>443600</v>
+      </c>
+      <c r="I9" s="3">
         <v>430300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>415900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>417400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>401600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>390200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>387200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>385300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>360800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>337500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>296100</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E10" s="3">
         <v>106300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>102000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>92700</v>
       </c>
-      <c r="G10" s="3">
-        <v>95800</v>
-      </c>
       <c r="H10" s="3">
+        <v>96600</v>
+      </c>
+      <c r="I10" s="3">
         <v>91400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>87700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>81000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>80100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>72500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>73900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>66600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>91800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>88700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>92200</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -892,8 +904,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -939,8 +952,11 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,102 +1002,111 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-11500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>15300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>23900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>42800</v>
       </c>
-      <c r="H14" s="3">
-        <v>3500</v>
-      </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-20500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-3400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>41000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>22700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E15" s="3">
         <v>49200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>41900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>41100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>46900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>44200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>45300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>42800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>44000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>49300</v>
-      </c>
-      <c r="M15" s="3">
-        <v>44700</v>
       </c>
       <c r="N15" s="3">
         <v>44700</v>
       </c>
       <c r="O15" s="3">
+        <v>44700</v>
+      </c>
+      <c r="P15" s="3">
         <v>45300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>40400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>564400</v>
+      </c>
+      <c r="E17" s="3">
         <v>530400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>496200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>500300</v>
       </c>
-      <c r="G17" s="3">
-        <v>503400</v>
-      </c>
       <c r="H17" s="3">
+        <v>502600</v>
+      </c>
+      <c r="I17" s="3">
         <v>486400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>472900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>472000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>456900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>450800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>443700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>443100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>473700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>425100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>380500</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E18" s="3">
         <v>43000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>45100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>38400</v>
       </c>
-      <c r="G18" s="3">
-        <v>36800</v>
-      </c>
       <c r="H18" s="3">
+        <v>37600</v>
+      </c>
+      <c r="I18" s="3">
         <v>35200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>30600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>26400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>24800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-21100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,231 +1241,244 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1500</v>
+        <v>-400</v>
       </c>
       <c r="E20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-3600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-4300</v>
-      </c>
       <c r="H20" s="3">
-        <v>4100</v>
+        <v>-3500</v>
       </c>
       <c r="I20" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J20" s="3">
         <v>-3600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>18100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>93700</v>
+        <v>96100</v>
       </c>
       <c r="E21" s="3">
+        <v>93600</v>
+      </c>
+      <c r="F21" s="3">
         <v>90600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>81700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>88100</v>
       </c>
-      <c r="H21" s="3">
-        <v>75400</v>
-      </c>
       <c r="I21" s="3">
+        <v>74700</v>
+      </c>
+      <c r="J21" s="3">
         <v>79500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>77000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>63300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>64600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>70800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>55900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>30300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>59700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E22" s="3">
         <v>20400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>22900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>30300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>30400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>30600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>36400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>41200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>42000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>41000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>39000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>34300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>26800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E23" s="3">
         <v>35500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-31900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-11500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-27500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-49200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15300</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-21100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
-      </c>
-      <c r="L24" s="3">
-        <v>300</v>
       </c>
       <c r="M24" s="3">
         <v>300</v>
       </c>
       <c r="N24" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
@@ -1442,10 +1487,13 @@
         <v>100</v>
       </c>
       <c r="Q24" s="3">
+        <v>100</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E26" s="3">
         <v>56600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-32400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-11900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-27600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-49300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15500</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E27" s="3">
         <v>55900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-31800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-27400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-47500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,102 +1839,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="E32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F32" s="3">
         <v>3600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2200</v>
       </c>
-      <c r="G32" s="3">
-        <v>4300</v>
-      </c>
       <c r="H32" s="3">
-        <v>-4100</v>
+        <v>3500</v>
       </c>
       <c r="I32" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="J32" s="3">
         <v>3600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E33" s="3">
         <v>55900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-31800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-27400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-47500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E35" s="3">
         <v>55900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-31800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-27400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-47500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,91 +2136,95 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>114800</v>
+      </c>
+      <c r="E41" s="3">
         <v>147400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>133500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>86100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>76700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>67900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>77000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>43400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>48400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>41300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>65100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>79400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>5900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4800</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -2145,337 +2234,361 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>253500</v>
+      </c>
+      <c r="E43" s="3">
         <v>237300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>272800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>271100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>258600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>253900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>250300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>264400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>232900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>216400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>194200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>191700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>137500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>136000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>136800</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E44" s="3">
         <v>20200</v>
-      </c>
-      <c r="E44" s="3">
-        <v>19400</v>
       </c>
       <c r="F44" s="3">
         <v>19400</v>
       </c>
       <c r="G44" s="3">
+        <v>19400</v>
+      </c>
+      <c r="H44" s="3">
         <v>19500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>20200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>20000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>20700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>19500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>22000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>19100</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E45" s="3">
         <v>34900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>34800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>29900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>37100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>32700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31200</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>479500</v>
+      </c>
+      <c r="E46" s="3">
         <v>476900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>497600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>456000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>432300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>423800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>410900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>447900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>377800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>362600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>343100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>330200</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>95800</v>
+      </c>
+      <c r="E47" s="3">
         <v>95200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>103000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>103800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>105200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>106400</v>
-      </c>
-      <c r="I47" s="3">
-        <v>107400</v>
       </c>
       <c r="J47" s="3">
         <v>107400</v>
       </c>
       <c r="K47" s="3">
+        <v>107400</v>
+      </c>
+      <c r="L47" s="3">
         <v>107500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>106700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>106200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>99400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>92600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>91500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4318800</v>
+      </c>
+      <c r="E48" s="3">
         <v>3739300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3494000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3490400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3530600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3709000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3686900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3700300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3653300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3664600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3747100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3839100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3858000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3789100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3606300</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>488200</v>
+      </c>
+      <c r="E49" s="3">
         <v>416300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>390800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>391400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>396400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>412700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>414400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>422800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>415400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>431800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>445600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>454200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>467900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>492900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>447600</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,8 +2684,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2606,17 +2725,20 @@
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" s="3">
         <v>123900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>129000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>131100</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2784,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5426200</v>
+      </c>
+      <c r="E54" s="3">
         <v>4770300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4506700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4464100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4488100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4677000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4644600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4703400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4577900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4588900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4666400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4747700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4786700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4758600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4523900</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,290 +2876,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>101400</v>
+      </c>
+      <c r="E57" s="3">
         <v>86900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>79400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>79100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>78700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>82900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>79400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>108400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>89600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>85700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>74200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>81300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>243800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>235500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>192900</v>
+      </c>
+      <c r="E58" s="3">
         <v>14100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>34700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>54500</v>
       </c>
-      <c r="G58" s="3">
-        <v>64400</v>
-      </c>
       <c r="H58" s="3">
+        <v>900</v>
+      </c>
+      <c r="I58" s="3">
         <v>46100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>170500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>414700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>312200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>380800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>399600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>493500</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>85400</v>
+      </c>
+      <c r="E59" s="3">
         <v>71500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>63300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>63800</v>
       </c>
-      <c r="G59" s="3">
-        <v>63700</v>
-      </c>
       <c r="H59" s="3">
+        <v>63000</v>
+      </c>
+      <c r="I59" s="3">
         <v>61300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>55500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>33700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>42500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>39100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>43000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>43800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>273100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>260400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>511200</v>
+      </c>
+      <c r="E60" s="3">
         <v>312300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>308700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>327300</v>
       </c>
-      <c r="G60" s="3">
-        <v>323500</v>
-      </c>
       <c r="H60" s="3">
+        <v>259300</v>
+      </c>
+      <c r="I60" s="3">
         <v>316100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>424700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>672800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>555100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>618000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>623900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>726200</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1494200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1683700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1682800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1778000</v>
       </c>
-      <c r="G61" s="3">
-        <v>1807200</v>
-      </c>
       <c r="H61" s="3">
+        <v>1870700</v>
+      </c>
+      <c r="I61" s="3">
         <v>2049300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2061000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1833900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2483800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2386800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2429400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2369900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2560000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2472000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2422300</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E62" s="3">
         <v>23500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28100</v>
       </c>
-      <c r="G62" s="3">
-        <v>13900</v>
-      </c>
       <c r="H62" s="3">
+        <v>14600</v>
+      </c>
+      <c r="I62" s="3">
         <v>30900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>31700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>31400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>41000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>34600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>42500</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3324,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2065600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2050400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2044000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2159300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2183900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2419800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2540500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2560600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3118800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3055200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3110100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3160800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3386600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3291400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3006700</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3594,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1559300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1523300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1536300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1504900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1458100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1386800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1344300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1313200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1276200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1232200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1209600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1180700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1138300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1064300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1024300</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3794,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3320600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2678200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2421000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2262400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2261200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2207500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1933400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1960900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1270300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1314200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1335800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1363700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1400100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1467300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1517200</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E81" s="3">
         <v>55900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-31800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-27400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-47500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,55 +4021,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E83" s="3">
         <v>37600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>36200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>37800</v>
       </c>
-      <c r="G83" s="3">
-        <v>49600</v>
-      </c>
       <c r="H83" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I83" s="3">
         <v>45600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>55100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>36700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>57300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>29000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>42000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>35200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>45200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>40400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>55200</v>
+      </c>
+      <c r="E89" s="3">
         <v>107200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>71500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>60600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>59500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>63100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>59400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>25800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>29100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>23900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>34300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>57300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,55 +4391,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-32400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-48100</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="G91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="3">
-        <v>-29700</v>
-      </c>
       <c r="H91" s="3">
+        <v>62300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-23900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-38400</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-25400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-22300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-30600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-21500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-18300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-69900</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4539,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-710000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-278500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-62100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-32800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>87200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-60300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>11000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>43000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-33300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>4000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-25200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,31 +4611,32 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E96" s="3">
         <v>41200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>39900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>39500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>38300</v>
-      </c>
-      <c r="H96" s="3">
-        <v>33000</v>
       </c>
       <c r="I96" s="3">
         <v>33000</v>
       </c>
       <c r="J96" s="3">
-        <v>16600</v>
+        <v>33000</v>
       </c>
       <c r="K96" s="3">
         <v>16600</v>
@@ -4415,19 +4648,22 @@
         <v>16600</v>
       </c>
       <c r="N96" s="3">
+        <v>16600</v>
+      </c>
+      <c r="O96" s="3">
         <v>26500</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,60 +4809,66 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>622200</v>
+      </c>
+      <c r="E100" s="3">
         <v>185700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>33100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-23800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-140000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-26000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>45000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-51600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-57300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-14300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-50900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -4632,80 +4880,86 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E102" s="3">
         <v>14400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>42500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-26900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>33700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-23700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>20100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-15000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AHR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>AHR</t>
   </si>
@@ -656,237 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>651600</v>
+      </c>
+      <c r="E8" s="3">
         <v>604700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>573400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>541300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>538800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>540200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>521700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>503500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>498300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>481800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>462700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>461100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>451900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>452600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>426200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>388300</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>525300</v>
+      </c>
+      <c r="E9" s="3">
         <v>492500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>467100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>439300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>446100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>443600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>430300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>415900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>417400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>401600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>390200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>387200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>385300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>360800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>337500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>296100</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>126300</v>
+      </c>
+      <c r="E10" s="3">
         <v>112200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>106300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>102000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>92700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>96600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>91400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>87700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>81000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>80100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>72500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>73900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>66600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>91800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>88700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>92200</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,108 +1022,117 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E14" s="3">
         <v>12400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-11500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>15300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>23900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>42800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2900</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-20500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-3400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>41000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>22700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E15" s="3">
         <v>55300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>49200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>41900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>41100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>46900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>44200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>45300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>42800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>44000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>49300</v>
-      </c>
-      <c r="N15" s="3">
-        <v>44700</v>
       </c>
       <c r="O15" s="3">
         <v>44700</v>
       </c>
       <c r="P15" s="3">
+        <v>44700</v>
+      </c>
+      <c r="Q15" s="3">
         <v>45300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>40400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>609900</v>
+      </c>
+      <c r="E17" s="3">
         <v>564400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>530400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>496200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>500300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>502600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>486400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>472900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>472000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>456900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>450800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>443700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>443100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>473700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>425100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>380500</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E18" s="3">
         <v>40400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>43000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>45100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>38400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>37600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>35200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>30600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>26400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,246 +1275,259 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>18100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>111700</v>
+      </c>
+      <c r="E21" s="3">
         <v>96100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>93600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>90600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>81700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>88100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>74700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>79500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>77000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>63300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>64600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>70800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>55900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>30300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>59700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E22" s="3">
         <v>19800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>20400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>22600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>30300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>30400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>30600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>36400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>41200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>42000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>41000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>39000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>34300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>26800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E23" s="3">
         <v>8500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>35500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-31900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-31100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-27500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-49200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-15300</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-21100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>300</v>
       </c>
       <c r="N24" s="3">
         <v>300</v>
       </c>
       <c r="O24" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P24" s="3">
         <v>100</v>
@@ -1490,10 +1536,13 @@
         <v>100</v>
       </c>
       <c r="R24" s="3">
+        <v>100</v>
+      </c>
+      <c r="S24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E26" s="3">
         <v>10900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>56600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-32400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-11900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-27600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-49300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-15500</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E27" s="3">
         <v>10800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>55900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-31800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-25900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-47500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-13500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-18100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E33" s="3">
         <v>10800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>55900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-31800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-25900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-47500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-13500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E35" s="3">
         <v>10800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>55900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-31800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-25900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-47500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-13500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,97 +2223,101 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>119400</v>
+      </c>
+      <c r="E41" s="3">
         <v>114800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>147400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>133500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>86100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>76700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>67900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>52100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>77000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>43400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>35200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>48400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>41300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>65100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>79400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>5900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4800</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -2237,358 +2327,382 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>291400</v>
+      </c>
+      <c r="E43" s="3">
         <v>253500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>237300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>272800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>271100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>258600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>253900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>250300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>264400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>232900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>216400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>194200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>191700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>137500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>136000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>136800</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E44" s="3">
         <v>18800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>20200</v>
-      </c>
-      <c r="F44" s="3">
-        <v>19400</v>
       </c>
       <c r="G44" s="3">
         <v>19400</v>
       </c>
       <c r="H44" s="3">
+        <v>19400</v>
+      </c>
+      <c r="I44" s="3">
         <v>19500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>20200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>20000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>20700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>19500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>22000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>19300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>19100</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E45" s="3">
         <v>55400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>34900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>34800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>37500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>29900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>37100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>32700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>31200</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>521800</v>
+      </c>
+      <c r="E46" s="3">
         <v>479500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>476900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>497600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>456000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>432300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>423800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>410900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>447900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>377800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>362600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>343100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>330200</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>96700</v>
+      </c>
+      <c r="E47" s="3">
         <v>95800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>95200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>103000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>103800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>105200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>106400</v>
-      </c>
-      <c r="J47" s="3">
-        <v>107400</v>
       </c>
       <c r="K47" s="3">
         <v>107400</v>
       </c>
       <c r="L47" s="3">
+        <v>107400</v>
+      </c>
+      <c r="M47" s="3">
         <v>107500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>106700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>106200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>99400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>92600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>91500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>104500</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4450300</v>
+      </c>
+      <c r="E48" s="3">
         <v>4318800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3739300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3494000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3490400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3530600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3709000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3686900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3700300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3653300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3664600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3747100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3839100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3858000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3789100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3606300</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>485400</v>
+      </c>
+      <c r="E49" s="3">
         <v>488200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>416300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>390800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>391400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>396400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>412700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>414400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>422800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>415400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>431800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>445600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>454200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>467900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>492900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>447600</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2804,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2728,17 +2848,20 @@
       <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="3">
         <v>123900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>129000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>131100</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5598700</v>
+      </c>
+      <c r="E54" s="3">
         <v>5426200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4770300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4506700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4464100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4488100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4677000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4644600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4703400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4577900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4588900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4666400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4747700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4786700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4758600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4523900</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,308 +3007,327 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E57" s="3">
         <v>101400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>86900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>79400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>79100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>78700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>82900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>79400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>108400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>89600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>85700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>74200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>81300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>243800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>235500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>178600</v>
+      </c>
+      <c r="E58" s="3">
         <v>192900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>34700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>54500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>46100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>170500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>414700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>312200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>380800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>399600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>493500</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E59" s="3">
         <v>85400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>71500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>63300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>63800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>63000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>61300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>55500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>33700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>42500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>39100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>43000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>43800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>273100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>260400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>519300</v>
+      </c>
+      <c r="E60" s="3">
         <v>511200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>312300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>308700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>327300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>259300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>316100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>424700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>672800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>555100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>618000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>623900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>726200</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1498100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1494200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1683700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1682800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1778000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1870700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2049300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2061000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1833900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2483800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2386800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2429400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2369900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2560000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2472000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2422300</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E62" s="3">
         <v>7900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>23500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>26600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>28100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>30900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>31700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>31400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>41000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>29500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>34600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>42500</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2077300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2065600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2050400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2044000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2159300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2183900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2419800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2540500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2560600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3118800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3055200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3110100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3160800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3386600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3291400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3006700</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1583400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1559300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1523300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1536300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1504900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1458100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1386800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1344300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1313200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1276200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1232200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1209600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1180700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1138300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1064300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1024300</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3481700</v>
+      </c>
+      <c r="E76" s="3">
         <v>3320600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2678200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2421000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2262400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2261200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2207500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1933400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1960900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1270300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1314200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1335800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1363700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1400100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1467300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1517200</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E81" s="3">
         <v>10800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>55900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-31800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-25900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-47500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-13500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,58 +4220,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E83" s="3">
         <v>42400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>37600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>36200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>37800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>45600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>55100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>36700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>57300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>29000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>42000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>35200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>45200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>40400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>81100</v>
+      </c>
+      <c r="E89" s="3">
         <v>55200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>107200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>71500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>60600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>59500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>63100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>59400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>25800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>29100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>19800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>23900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>34300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>57300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,58 +4612,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>80400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-32400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-48100</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="H91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>62300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-23900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-38400</v>
       </c>
-      <c r="K91" s="3" t="s">
+      <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-22300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-30600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-21500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-69900</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-203100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-710000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-278500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-62100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-32800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>87200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-30400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-60300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>11000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>43000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-33300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>4000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-25200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,34 +4845,35 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E96" s="3">
         <v>42900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>41200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>39900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>39500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>38300</v>
-      </c>
-      <c r="I96" s="3">
-        <v>33000</v>
       </c>
       <c r="J96" s="3">
         <v>33000</v>
       </c>
       <c r="K96" s="3">
-        <v>16600</v>
+        <v>33000</v>
       </c>
       <c r="L96" s="3">
         <v>16600</v>
@@ -4651,19 +4885,22 @@
         <v>16600</v>
       </c>
       <c r="O96" s="3">
+        <v>16600</v>
+      </c>
+      <c r="P96" s="3">
         <v>26500</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,67 +5055,73 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>127200</v>
+      </c>
+      <c r="E100" s="3">
         <v>622200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>185700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>33100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-23800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-140000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-26000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>45000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-51600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-57300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-14300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-50900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-12000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
@@ -4883,83 +5132,89 @@
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-32600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>14400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>42500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>19100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-26900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>33700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-23700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>20100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-15000</v>
       </c>
     </row>
